--- a/fixed_allocation_daily_bear.xlsx
+++ b/fixed_allocation_daily_bear.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,6 +648,1230 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-09-12T18:26:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.2548</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.5427999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.2724</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.4309</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-09-12T18:34:39</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.2516</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.5247000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.2691</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.4259</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-09-12T18:42:31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2194</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.4641</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.235</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-09-12T18:50:25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.2494</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.5602</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.2668</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.4213</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-09-12T18:58:14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.2369</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.5145999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.2536</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.418</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:06:09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.2471</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.5264</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.2644</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.4241</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:14:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.249</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.5459000000000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2663</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.4331</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:21:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.2268</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.4931</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.2429</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.4029</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:29:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2371</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.4894</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2538</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.424</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:34:52</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FIXED_ppo_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ppo</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2114</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.4453</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.2266</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.3885</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-09-12T19:56:16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2337</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.5021</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.2501</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.4114</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:02:56</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.229</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.4837</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.2451</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.4077</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:09:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.2266</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.4741</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.2426</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.4076</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:15:41</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.2307</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.4891</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.4121</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:23:24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.2331</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.4964</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2495</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.4112</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:31:39</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.2282</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.4816</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.2444</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.4088</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:38:15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.2297</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.4851</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.2459</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.4087</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:44:56</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2339</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.4988</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.2504</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.4112</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-09-12T20:53:07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.2308</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.4886</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.2471</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.4095</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-09-12T21:00:11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.2319</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.4912</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.2483</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.4119</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-09-12T21:06:38</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>trial_011</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.2303</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2466</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.4089</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 323}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-09-12T21:14:19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>trial_012</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2287</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.4815</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.2448</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.4104</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 324}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-09-12T21:21:54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>trial_013</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.2291</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.4836</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.2453</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0646</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.4088</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 325}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-09-12T21:28:12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FIXED_sac_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>trial_014</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.2303</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.4868</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2465</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.4087</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 326}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixed_allocation_daily_bear.xlsx
+++ b/fixed_allocation_daily_bear.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,6 +1872,1026 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:45:04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>trial_000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.2223</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.471</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.2381</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.4164</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 312}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:50:51</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.2834</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.6506999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.3026</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4195</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.4346</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-09-13T08:56:24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2847</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.6846</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.3039</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.4432</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:02:03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-0.5514</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-0.2674</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.4272</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:07:12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.2487</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.5235</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.4269</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:12:24</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.2897</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.694</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.3092</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.0191</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.438</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:18:02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.3079</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.8065</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.3283</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-0.4359</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:23:36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.3231</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.7668</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.3443</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.06519999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-0.4546</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:29:26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.2504</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.5392</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.2678</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-0.4362</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:35:03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FIXED_ddpg_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ddpg</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.2732</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.6454</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.2919</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.4127</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:41:26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>trial_001</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2675</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.5939</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.2858</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-0.4271</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 313}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:46:58</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>trial_002</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.2494</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.5357</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.2668</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.4147</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 314}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:52:30</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>trial_003</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.3096</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.7674</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.3301</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.4441</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 315}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-09-13T09:57:52</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>trial_004</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.2868</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.7241</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.3062</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.422</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 316}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:03:36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>trial_005</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.2025</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.4018</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.217</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.3944</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 317}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:09:16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>trial_006</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.259</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.6178</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.2769</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 318}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:14:53</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>trial_007</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.5084</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.2643</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-0.428</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 319}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:20:26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>trial_008</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.2646</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.6098</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.2828</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.4263</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 320}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:25:57</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>trial_009</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.2769</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.6169</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-0.4504</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 321}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-09-13T10:31:27</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIXED_td3_allocation_daily_bear_runs_batch</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>trial_010</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>td3</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.2817</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.6145</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.3009</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.4566</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-0.3943</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>{"erl": {"learning_rate": 1.3204392685000274e-05, "batch_size": 512, "gamma": 0.9954379276836015, "net_dimension": 256, "net_dims": [256, 256], "target_step": 8192, "horizon_len": 2048, "repeat_times": 2.0, "buffer_size": 1000000, "buffer_init_size": 2048, "eval_gap": 64, "eval_times": 16, "if_use_per": false, "seed": 322}, "task": "allocation", "freq": "daily", "dataset": "bear"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
